--- a/outputs/evaluation/requirement/validation/gemini-3-5-flash-lite/CF_M09/first/CF_M09_req_eval.xlsx
+++ b/outputs/evaluation/requirement/validation/gemini-3-5-flash-lite/CF_M09/first/CF_M09_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>0.9833</v>
       </c>
       <c r="D13" t="n">
+        <v>0.9916</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.8996</v>
       </c>
     </row>
@@ -755,10 +763,6 @@
           <t>Ver todos los activos de los que dispongo</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>FR</t>
@@ -772,10 +776,6 @@
           <t>View all the assets I have available</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -806,14 +806,11 @@
           <t>Se debe poder escoger los activos intervenidos</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>R_30</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -827,14 +824,11 @@
           <t>It must be possible to choose the intervened assets.</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>CF_M09_R30</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -865,14 +859,11 @@
           <t>Se debe poder añadir al activo todos los atributos de activo y de tipo de activo</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>R_08</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -886,14 +877,11 @@
           <t>All asset and asset type attributes can be added to the asset.</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>CF_M09_R08</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -924,14 +912,11 @@
           <t>Se elimina el activo de la lista automáticamente</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -945,14 +930,11 @@
           <t>The asset is automatically removed from the list.</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>CF_M09_R12</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -983,14 +965,11 @@
           <t>Ningún usuario puede ver activos de los que no disponga (menos administradores, que ven todos)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>R_27</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1004,14 +983,11 @@
           <t>No user can see assets they do not own (except administrators, who see all).</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>CF_M09_R27</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1042,10 +1018,6 @@
           <t>Ver los activos que hay distribuidos en una location</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1059,10 +1031,6 @@
           <t>View the assets that are distributed across a location</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1093,14 +1061,11 @@
           <t>Se debe poder ver los detalles de cada activo</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>R_27</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1114,14 +1079,11 @@
           <t>You should be able to see the details of each asset</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>CF_M09_R27</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1152,14 +1114,11 @@
           <t>Se debe poder ver los detalles de cada activo</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>R_23</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1173,14 +1132,11 @@
           <t>You should be able to see the details of each asset</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>CF_M09_R23</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1211,14 +1167,11 @@
           <t>Se debe poder ver los detalles de cada activo</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1232,14 +1185,11 @@
           <t>You should be able to see the details of each asset</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>CF_M09_R20</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1270,10 +1220,6 @@
           <t>Modificar la información de un activo</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1287,10 +1233,6 @@
           <t>Modify asset information</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1321,10 +1263,6 @@
           <t>Eliminar activos de un spot</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1338,10 +1276,6 @@
           <t>Remove assets from a spot</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1372,14 +1306,11 @@
           <t>Cada activo se asociará a una acción</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>R_30</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1393,14 +1324,11 @@
           <t>Each asset will be associated with an action.</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>CF_M09_R30</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1431,14 +1359,11 @@
           <t>Debe poderse consultar el registro a nivel de location o a nivel de activo</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>R_40</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1452,14 +1377,11 @@
           <t>It must be possible to consult the registry at the location level or at the asset level.</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>CF_M09_R40</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1490,10 +1412,6 @@
           <t>Crear activos asignados a un spot</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1507,10 +1425,6 @@
           <t>Create assets assigned to a spot</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1541,14 +1455,11 @@
           <t>Solo se puede eliminar un activo si no está asignado a una intervención</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1562,14 +1473,11 @@
           <t>An asset can only be deleted if it is not assigned to an intervention.</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>CF_M09_R12</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1600,14 +1508,11 @@
           <t>Se puede modificar cualquier atributo del activo</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>R_15</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1621,14 +1526,11 @@
           <t>Any attribute of the asset can be modified.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>CF_M09_R15</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1659,14 +1561,11 @@
           <t>Se puede dejar en blanco el número de serie, en cuyo caso se asignará en la instalación</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>R_08</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1680,14 +1579,11 @@
           <t>The serial number can be left blank, in which case it will be assigned during installation.</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>CF_M09_R08</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1718,14 +1614,11 @@
           <t>No se pueden mostrar activos fuera de la location</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>R_23</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1739,14 +1632,11 @@
           <t>Assets cannot be displayed outside of the location</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>CF_M09_R23</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1777,14 +1667,11 @@
           <t>No se pueden mostrar activos fuera de la location</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1798,14 +1685,11 @@
           <t>Assets cannot be displayed outside of the location</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>CF_M09_R20</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1836,14 +1720,11 @@
           <t>Los usuarios sin permiso no pueden acceder a ver y editar activos.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>R_56</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1857,14 +1738,11 @@
           <t>Users without permission cannot access to view and edit assets.</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>CF_M09_R56</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1895,10 +1773,6 @@
           <t>Ver los activos que hay distribuidos en una location en forma de mapa 3D</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1912,10 +1786,6 @@
           <t>View the assets that are distributed across a location in 3D map format</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1946,14 +1816,11 @@
           <t>La plataforma escala de forma dinámica con los cambios de conexiones simultáneas.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>R_52</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1967,14 +1834,11 @@
           <t>The platform scales dynamically with changes in simultaneous connections.</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>CF_M09_R52</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2005,14 +1869,11 @@
           <t>Se ve el spot creado automáticamente</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2026,14 +1887,11 @@
           <t>The created spot is automatically displayed.</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>CF_M09_R01</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2064,14 +1922,11 @@
           <t>No se deben poder incluir activos que no están en la location o que ya están en una intervención</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>R_30</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2085,14 +1940,11 @@
           <t>It should not be possible to include assets that are not in the location or that they are already in an intervention</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>CF_M09_R30</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2123,14 +1975,11 @@
           <t>Solo se puede eliminar una intervención si no está finalizada</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>R_34</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2144,14 +1993,11 @@
           <t>An intervention can only be removed if it is not completed.</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>CF_M09_R34</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2182,14 +2028,11 @@
           <t>No se puede eliminar un spot si tiene activos asignados</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>R_05</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2203,14 +2046,11 @@
           <t>A spot cannot be deleted if it has assets assigned to it.</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>CF_M09_R05</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2241,10 +2081,6 @@
           <t>Eliminar una intervención</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2258,10 +2094,6 @@
           <t>Remove an intervention</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2297,9 +2129,6 @@
           <t>C_07</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2323,8 +2152,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2355,10 +2182,6 @@
           <t>Crear una nueva intervención</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2372,10 +2195,6 @@
           <t>Create a new intervention</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2406,14 +2225,11 @@
           <t>Se puede modificar el spot al que está asignado</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>R_15</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2427,14 +2243,11 @@
           <t>You can change the spot it is assigned to</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>CF_M09_R15</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2465,10 +2278,6 @@
           <t>Ver el historial de intervenciones realizadas</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2482,10 +2291,6 @@
           <t>See the history of interventions carried out</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2516,10 +2321,6 @@
           <t>Crear nuevos spots en una location</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2533,10 +2334,6 @@
           <t>Create new spots in a location</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2567,10 +2364,6 @@
           <t>Eliminar spots de una location</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2584,10 +2377,6 @@
           <t>Remove spots from a location</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2623,9 +2412,6 @@
           <t>C_06</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2649,8 +2435,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2681,10 +2465,6 @@
           <t>Introducir el ID del mapa 3D</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2698,10 +2478,6 @@
           <t>Introduce the ID of the 3D map</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2732,14 +2508,11 @@
           <t>Para poder finalizar la intervención se tendrá que rellenar toda la información exigida</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>R_37</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2753,14 +2526,11 @@
           <t>In order to complete the intervention, you will have to fill in all the required information</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>CF_M09_R37</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2796,9 +2566,6 @@
           <t>C_03</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2822,8 +2589,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2854,14 +2619,11 @@
           <t>Ningún usuario puede ver información más allá de la suya propia.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>R_58</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2875,14 +2637,11 @@
           <t>No user can see information beyond their own.</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>CF_M09_R58</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2913,10 +2672,6 @@
           <t>Realizar y completar una intervención</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2930,10 +2685,6 @@
           <t>Perform and complete an intervention</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2964,14 +2715,11 @@
           <t>El sistema responde a cualquier acción del usuario en menos de cinco segundos.</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>R_48</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2985,14 +2733,11 @@
           <t>The system responds to any user action in less than five seconds.</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>CF_M09_R48</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3023,14 +2768,11 @@
           <t>No se puede introducir un nuevo ID una vez asignado</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>R_18</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3044,14 +2786,11 @@
           <t>A new ID cannot be introduced once assigned.</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>CF_M09_R18</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3082,14 +2821,11 @@
           <t>Se debe ver toda la información de la intervención de forma sencilla</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>R_37</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3103,14 +2839,11 @@
           <t>You must see all the information of the intervention in a simple way</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>CF_M09_R37</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3141,14 +2874,11 @@
           <t>La interfaz se puede entender por cualquier persona que hable uno de los 7 idiomas y el idioma por defecto es el inglés.</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>R_44</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3162,14 +2892,11 @@
           <t>The interface can be understood by any person who speaks one of the 7 languages and the default language is English.</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>CF_M09_R44</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3200,14 +2927,11 @@
           <t>La información debe ser la misma que en la vista de lista</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>R_23</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3221,14 +2945,11 @@
           <t>The information must be the same as in the view of list</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>CF_M09_R23</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3264,9 +2985,6 @@
           <t>C_04</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>QR</t>
@@ -3290,8 +3008,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3327,9 +3043,6 @@
           <t>C_09</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>QR</t>
@@ -3353,8 +3066,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3390,9 +3101,6 @@
           <t>C_08</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>QR</t>
@@ -3416,8 +3124,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3448,14 +3154,11 @@
           <t>Se elimina la intervención de la lista automáticamente</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>R_34</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3469,14 +3172,11 @@
           <t>The intervention is automatically removed from the list.</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>CF_M09_R34</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3507,14 +3207,11 @@
           <t>Los usuarios técnicos aprenden a usar las funcionalidades de la plataforma en menos de 30 minutos.</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>R_46</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3528,14 +3225,11 @@
           <t>Technical users learn to use the platform's functionalities in less than 30 minutes.</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>CF_M09_R46</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3566,14 +3260,11 @@
           <t>Se elimina el spot de la lista automáticamente</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>R_05</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3587,14 +3278,11 @@
           <t>The spot is automatically removed from the list.</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>CF_M09_R05</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3625,14 +3313,11 @@
           <t>Cualquier usuario puede acceder a la plataforma en cualquier momento del día. A excepción de actualizaciones programadas.</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>R_50</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3646,14 +3331,11 @@
           <t>Any user can access the platform at any time of day, except for scheduled updates.</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>CF_M09_R50</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3689,9 +3371,6 @@
           <t>C_05</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>QR</t>
@@ -3715,8 +3394,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3752,9 +3429,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>QR</t>
@@ -3778,8 +3452,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3810,14 +3482,11 @@
           <t>Se puede asignar un nombre a cada spot</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3831,14 +3500,11 @@
           <t>Each spot can be assigned a name.</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>CF_M09_R01</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3869,14 +3535,11 @@
           <t>La interfaz se adapta a pantalla de ordenador, tableta y móvil.</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>R_54</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3890,14 +3553,11 @@
           <t>The interface adapts to computer, tablet, and mobile screens.</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>CF_M09_R54</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3928,14 +3588,11 @@
           <t>Se asigna automáticamente el spot, aunque se puede decidir en qué spot se quiere asignar</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>R_08</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3949,14 +3606,11 @@
           <t>The spot is automatically assigned, although you can decide which spot you want to assign</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>CF_M09_R08</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3987,14 +3641,11 @@
           <t>Todos los colores usados en la interfaz se corresponden con los definidos en la paleta de color de Waapiti incluida en el código de la plataforma.</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>R_42</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -4008,14 +3659,11 @@
           <t>All colors used in the interface correspond to those defined in the Waapiti color palette included in the platform code.</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>CF_M09_R42</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4051,9 +3699,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>QR</t>
@@ -4077,8 +3722,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4109,14 +3752,11 @@
           <t>Se asigna automáticamente la planta o se pueden crear nuevas</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -4130,14 +3770,11 @@
           <t>The plant is automatically assigned or new ones can be created</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>CF_M09_R01</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
